--- a/Result/checksun_type/特殊照明業.xlsx
+++ b/Result/checksun_type/特殊照明業.xlsx
@@ -873,7 +873,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1057,15 +1057,11 @@
           <t>50.96</t>
         </is>
       </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>51.47</t>
-        </is>
-      </c>
-      <c r="AN2" t="inlineStr">
-        <is>
-          <t>52.21</t>
-        </is>
+      <c r="AM2" t="n">
+        <v>51.47</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>52.21</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
@@ -1112,20 +1108,16 @@
           <t>17956885.0</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
-        <is>
-          <t>8950584.4</t>
-        </is>
+      <c r="AX2" t="n">
+        <v>8950584.4</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
           <t>8157639.2</t>
         </is>
       </c>
-      <c r="AZ2" t="inlineStr">
-        <is>
-          <t>6929587.06</t>
-        </is>
+      <c r="AZ2" t="n">
+        <v>6929587.06</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
@@ -1142,8 +1134,10 @@
           <t>693693.9518489158</t>
         </is>
       </c>
-      <c r="BD2" t="n">
-        <v>17956885</v>
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>17956885.0</t>
+        </is>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1309,7 +1303,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1493,15 +1487,11 @@
           <t>50.48999999999999</t>
         </is>
       </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>51.48</t>
-        </is>
-      </c>
-      <c r="AN3" t="inlineStr">
-        <is>
-          <t>52.22</t>
-        </is>
+      <c r="AM3" t="n">
+        <v>51.48</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>52.22</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
@@ -1548,20 +1538,16 @@
           <t>4197152.0</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>6275232.4</t>
-        </is>
+      <c r="AX3" t="n">
+        <v>6275232.4</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
           <t>6626872.5</t>
         </is>
       </c>
-      <c r="AZ3" t="inlineStr">
-        <is>
-          <t>7203813.28</t>
-        </is>
+      <c r="AZ3" t="n">
+        <v>7203813.28</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
@@ -1578,8 +1564,10 @@
           <t>-200974.9605394397</t>
         </is>
       </c>
-      <c r="BD3" t="n">
-        <v>4197152</v>
+      <c r="BD3" t="inlineStr">
+        <is>
+          <t>4197152.0</t>
+        </is>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -1745,7 +1733,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1929,15 +1917,11 @@
           <t>50.38</t>
         </is>
       </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>51.58</t>
-        </is>
-      </c>
-      <c r="AN4" t="inlineStr">
-        <is>
-          <t>52.31</t>
-        </is>
+      <c r="AM4" t="n">
+        <v>51.58</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>52.31</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
@@ -1984,20 +1968,16 @@
           <t>5019179.0</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr">
-        <is>
-          <t>6863569.0</t>
-        </is>
+      <c r="AX4" t="n">
+        <v>6863569</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
           <t>6542082.1</t>
         </is>
       </c>
-      <c r="AZ4" t="inlineStr">
-        <is>
-          <t>7419548.0</t>
-        </is>
+      <c r="AZ4" t="n">
+        <v>7419548</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
@@ -2014,8 +1994,10 @@
           <t>2361.377496462315</t>
         </is>
       </c>
-      <c r="BD4" t="n">
-        <v>5019179</v>
+      <c r="BD4" t="inlineStr">
+        <is>
+          <t>5019179.0</t>
+        </is>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
@@ -2181,7 +2163,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2365,15 +2347,11 @@
           <t>50.5</t>
         </is>
       </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>51.71</t>
-        </is>
-      </c>
-      <c r="AN5" t="inlineStr">
-        <is>
-          <t>52.41</t>
-        </is>
+      <c r="AM5" t="n">
+        <v>51.71</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>52.41</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
@@ -2420,20 +2398,16 @@
           <t>8332853.0</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr">
-        <is>
-          <t>7339532.2</t>
-        </is>
+      <c r="AX5" t="n">
+        <v>7339532.2</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
           <t>6379937.7</t>
         </is>
       </c>
-      <c r="AZ5" t="inlineStr">
-        <is>
-          <t>7459733.34</t>
-        </is>
+      <c r="AZ5" t="n">
+        <v>7459733.34</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
@@ -2450,8 +2424,10 @@
           <t>204683.2040657345</t>
         </is>
       </c>
-      <c r="BD5" t="n">
-        <v>8332853</v>
+      <c r="BD5" t="inlineStr">
+        <is>
+          <t>8332853.0</t>
+        </is>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -2617,7 +2593,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -2801,15 +2777,11 @@
           <t>50.68</t>
         </is>
       </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>51.8</t>
-        </is>
-      </c>
-      <c r="AN6" t="inlineStr">
-        <is>
-          <t>52.5</t>
-        </is>
+      <c r="AM6" t="n">
+        <v>51.8</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>52.5</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
@@ -2856,20 +2828,16 @@
           <t>9246853.0</t>
         </is>
       </c>
-      <c r="AX6" t="inlineStr">
-        <is>
-          <t>6599368.2</t>
-        </is>
+      <c r="AX6" t="n">
+        <v>6599368.2</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
           <t>7443375.8</t>
         </is>
       </c>
-      <c r="AZ6" t="inlineStr">
-        <is>
-          <t>7455734.22</t>
-        </is>
+      <c r="AZ6" t="n">
+        <v>7455734.22</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
@@ -2886,8 +2854,10 @@
           <t>131367.7704480607</t>
         </is>
       </c>
-      <c r="BD6" t="n">
-        <v>9246853</v>
+      <c r="BD6" t="inlineStr">
+        <is>
+          <t>9246853.0</t>
+        </is>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
@@ -3053,7 +3023,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -3237,15 +3207,11 @@
           <t>50.86</t>
         </is>
       </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>51.85</t>
-        </is>
-      </c>
-      <c r="AN7" t="inlineStr">
-        <is>
-          <t>52.58</t>
-        </is>
+      <c r="AM7" t="n">
+        <v>51.85</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>52.58</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
@@ -3292,20 +3258,16 @@
           <t>4580125.0</t>
         </is>
       </c>
-      <c r="AX7" t="inlineStr">
-        <is>
-          <t>7364694.0</t>
-        </is>
+      <c r="AX7" t="n">
+        <v>7364694</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
           <t>7932550.0</t>
         </is>
       </c>
-      <c r="AZ7" t="inlineStr">
-        <is>
-          <t>7814412.12</t>
-        </is>
+      <c r="AZ7" t="n">
+        <v>7814412.12</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
@@ -3322,8 +3284,10 @@
           <t>-75988.84080747515</t>
         </is>
       </c>
-      <c r="BD7" t="n">
-        <v>4580125</v>
+      <c r="BD7" t="inlineStr">
+        <is>
+          <t>4580125.0</t>
+        </is>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
@@ -3489,7 +3453,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -3673,15 +3637,11 @@
           <t>51.27</t>
         </is>
       </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>51.96</t>
-        </is>
-      </c>
-      <c r="AN8" t="inlineStr">
-        <is>
-          <t>52.72</t>
-        </is>
+      <c r="AM8" t="n">
+        <v>51.96</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>52.72</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
@@ -3728,20 +3688,16 @@
           <t>7138835.0</t>
         </is>
       </c>
-      <c r="AX8" t="inlineStr">
-        <is>
-          <t>6978512.6</t>
-        </is>
+      <c r="AX8" t="n">
+        <v>6978512.6</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
           <t>8486901.6</t>
         </is>
       </c>
-      <c r="AZ8" t="inlineStr">
-        <is>
-          <t>7857936.62</t>
-        </is>
+      <c r="AZ8" t="n">
+        <v>7857936.62</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
@@ -3758,8 +3714,10 @@
           <t>130507.8874277407</t>
         </is>
       </c>
-      <c r="BD8" t="n">
-        <v>7138835</v>
+      <c r="BD8" t="inlineStr">
+        <is>
+          <t>7138835.0</t>
+        </is>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
@@ -3925,7 +3883,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -4109,15 +4067,11 @@
           <t>51.64</t>
         </is>
       </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>52.07</t>
-        </is>
-      </c>
-      <c r="AN9" t="inlineStr">
-        <is>
-          <t>52.85</t>
-        </is>
+      <c r="AM9" t="n">
+        <v>52.07</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>52.85</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
@@ -4164,20 +4118,16 @@
           <t>7398995.0</t>
         </is>
       </c>
-      <c r="AX9" t="inlineStr">
-        <is>
-          <t>6220595.2</t>
-        </is>
+      <c r="AX9" t="n">
+        <v>6220595.2</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
           <t>8095639.9</t>
         </is>
       </c>
-      <c r="AZ9" t="inlineStr">
-        <is>
-          <t>7785881.66</t>
-        </is>
+      <c r="AZ9" t="n">
+        <v>7785881.66</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
@@ -4194,8 +4144,10 @@
           <t>146694.7174984878</t>
         </is>
       </c>
-      <c r="BD9" t="n">
-        <v>7398995</v>
+      <c r="BD9" t="inlineStr">
+        <is>
+          <t>7398995.0</t>
+        </is>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
@@ -4361,7 +4313,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -4545,15 +4497,11 @@
           <t>51.84</t>
         </is>
       </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>52.13</t>
-        </is>
-      </c>
-      <c r="AN10" t="inlineStr">
-        <is>
-          <t>52.96</t>
-        </is>
+      <c r="AM10" t="n">
+        <v>52.13</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>52.96</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
@@ -4600,20 +4548,16 @@
           <t>4632033.0</t>
         </is>
       </c>
-      <c r="AX10" t="inlineStr">
-        <is>
-          <t>5420343.2</t>
-        </is>
+      <c r="AX10" t="n">
+        <v>5420343.2</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
           <t>7767470.7</t>
         </is>
       </c>
-      <c r="AZ10" t="inlineStr">
-        <is>
-          <t>7803894.44</t>
-        </is>
+      <c r="AZ10" t="n">
+        <v>7803894.44</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
@@ -4630,8 +4574,10 @@
           <t>136705.377688894</t>
         </is>
       </c>
-      <c r="BD10" t="n">
-        <v>4632033</v>
+      <c r="BD10" t="inlineStr">
+        <is>
+          <t>4632033.0</t>
+        </is>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
@@ -4797,7 +4743,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -4981,15 +4927,11 @@
           <t>51.82000000000001</t>
         </is>
       </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>52.17</t>
-        </is>
-      </c>
-      <c r="AN11" t="inlineStr">
-        <is>
-          <t>53.05</t>
-        </is>
+      <c r="AM11" t="n">
+        <v>52.17</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>53.05</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
@@ -5036,20 +4978,16 @@
           <t>13073482.0</t>
         </is>
       </c>
-      <c r="AX11" t="inlineStr">
-        <is>
-          <t>8287383.4</t>
-        </is>
+      <c r="AX11" t="n">
+        <v>8287383.4</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
           <t>7521303.8</t>
         </is>
       </c>
-      <c r="AZ11" t="inlineStr">
-        <is>
-          <t>7869389.7</t>
-        </is>
+      <c r="AZ11" t="n">
+        <v>7869389.7</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
@@ -5066,8 +5004,10 @@
           <t>414012.7716148719</t>
         </is>
       </c>
-      <c r="BD11" t="n">
-        <v>13073482</v>
+      <c r="BD11" t="inlineStr">
+        <is>
+          <t>13073482.0</t>
+        </is>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
@@ -5233,7 +5173,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -5417,15 +5357,11 @@
           <t>51.73999999999999</t>
         </is>
       </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>52.17</t>
-        </is>
-      </c>
-      <c r="AN12" t="inlineStr">
-        <is>
-          <t>53.14</t>
-        </is>
+      <c r="AM12" t="n">
+        <v>52.17</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>53.14</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
@@ -5472,20 +5408,16 @@
           <t>2649218.0</t>
         </is>
       </c>
-      <c r="AX12" t="inlineStr">
-        <is>
-          <t>8500406.0</t>
-        </is>
+      <c r="AX12" t="n">
+        <v>8500406</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
           <t>6617376.3</t>
         </is>
       </c>
-      <c r="AZ12" t="inlineStr">
-        <is>
-          <t>7740105.52</t>
-        </is>
+      <c r="AZ12" t="n">
+        <v>7740105.52</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
@@ -5502,8 +5434,10 @@
           <t>-109060.9431914054</t>
         </is>
       </c>
-      <c r="BD12" t="n">
-        <v>2649218</v>
+      <c r="BD12" t="inlineStr">
+        <is>
+          <t>2649218.0</t>
+        </is>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
@@ -5667,11 +5601,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="A13" t="inlineStr"/>
       <c r="B13" t="inlineStr">
         <is>
           <t>2459</t>
@@ -5853,41 +5783,37 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AM13" t="inlineStr">
+      <c r="AM13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO13" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="AN13" t="inlineStr">
+      <c r="AP13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AQ13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AR13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AS13" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AP13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AQ13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AR13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AS13" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="AT13" t="inlineStr">
         <is>
           <t>0</t>
@@ -5908,20 +5834,16 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AX13" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AX13" t="n">
+        <v>0</v>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AZ13" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ13" t="n">
+        <v>0</v>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
@@ -5938,8 +5860,10 @@
           <t>0</t>
         </is>
       </c>
-      <c r="BD13" t="n">
-        <v>0</v>
+      <c r="BD13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="BE13" t="inlineStr">
         <is>
@@ -6105,7 +6029,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -6289,15 +6213,11 @@
           <t>919.4</t>
         </is>
       </c>
-      <c r="AM14" t="inlineStr">
-        <is>
-          <t>948.95</t>
-        </is>
-      </c>
-      <c r="AN14" t="inlineStr">
-        <is>
-          <t>947.82</t>
-        </is>
+      <c r="AM14" t="n">
+        <v>948.95</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>947.8200000000001</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
@@ -6344,20 +6264,16 @@
           <t>10702402903.0</t>
         </is>
       </c>
-      <c r="AX14" t="inlineStr">
-        <is>
-          <t>13777681330.2</t>
-        </is>
+      <c r="AX14" t="n">
+        <v>13777681330.2</v>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
           <t>13184190874.5</t>
         </is>
       </c>
-      <c r="AZ14" t="inlineStr">
-        <is>
-          <t>14165986897.28</t>
-        </is>
+      <c r="AZ14" t="n">
+        <v>14165986897.28</v>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
@@ -6374,8 +6290,10 @@
           <t>-288049536.2624874</t>
         </is>
       </c>
-      <c r="BD14" t="n">
-        <v>10702402903</v>
+      <c r="BD14" t="inlineStr">
+        <is>
+          <t>10702402903.0</t>
+        </is>
       </c>
       <c r="BE14" t="inlineStr">
         <is>
@@ -6541,7 +6459,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -6725,15 +6643,11 @@
           <t>909.2</t>
         </is>
       </c>
-      <c r="AM15" t="inlineStr">
-        <is>
-          <t>954.7</t>
-        </is>
-      </c>
-      <c r="AN15" t="inlineStr">
-        <is>
-          <t>945.54</t>
-        </is>
+      <c r="AM15" t="n">
+        <v>954.7</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>945.54</v>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
@@ -6780,20 +6694,16 @@
           <t>9579043601.0</t>
         </is>
       </c>
-      <c r="AX15" t="inlineStr">
-        <is>
-          <t>13831910429.6</t>
-        </is>
+      <c r="AX15" t="n">
+        <v>13831910429.6</v>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
           <t>13509805904.0</t>
         </is>
       </c>
-      <c r="AZ15" t="inlineStr">
-        <is>
-          <t>14413977761.06</t>
-        </is>
+      <c r="AZ15" t="n">
+        <v>14413977761.06</v>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
@@ -6810,8 +6720,10 @@
           <t>-94238805.57345963</t>
         </is>
       </c>
-      <c r="BD15" t="n">
-        <v>9579043601</v>
+      <c r="BD15" t="inlineStr">
+        <is>
+          <t>9579043601.0</t>
+        </is>
       </c>
       <c r="BE15" t="inlineStr">
         <is>
@@ -6977,7 +6889,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -7161,15 +7073,11 @@
           <t>906.8</t>
         </is>
       </c>
-      <c r="AM16" t="inlineStr">
-        <is>
-          <t>962.95</t>
-        </is>
-      </c>
-      <c r="AN16" t="inlineStr">
-        <is>
-          <t>944.08</t>
-        </is>
+      <c r="AM16" t="n">
+        <v>962.95</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>944.08</v>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
@@ -7216,20 +7124,16 @@
           <t>16911194399.0</t>
         </is>
       </c>
-      <c r="AX16" t="inlineStr">
-        <is>
-          <t>14386844246.4</t>
-        </is>
+      <c r="AX16" t="n">
+        <v>14386844246.4</v>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
           <t>13675683609.2</t>
         </is>
       </c>
-      <c r="AZ16" t="inlineStr">
-        <is>
-          <t>14618581897.64</t>
-        </is>
+      <c r="AZ16" t="n">
+        <v>14618581897.64</v>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
@@ -7246,8 +7150,10 @@
           <t>306359263.681345</t>
         </is>
       </c>
-      <c r="BD16" t="n">
-        <v>16911194399</v>
+      <c r="BD16" t="inlineStr">
+        <is>
+          <t>16911194399.0</t>
+        </is>
       </c>
       <c r="BE16" t="inlineStr">
         <is>
@@ -7413,7 +7319,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -7597,15 +7503,11 @@
           <t>911.4</t>
         </is>
       </c>
-      <c r="AM17" t="inlineStr">
-        <is>
-          <t>971.8</t>
-        </is>
-      </c>
-      <c r="AN17" t="inlineStr">
-        <is>
-          <t>941.9</t>
-        </is>
+      <c r="AM17" t="n">
+        <v>971.8</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>941.9</v>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
@@ -7652,20 +7554,16 @@
           <t>15812987742.0</t>
         </is>
       </c>
-      <c r="AX17" t="inlineStr">
-        <is>
-          <t>13146559354.4</t>
-        </is>
+      <c r="AX17" t="n">
+        <v>13146559354.4</v>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
           <t>13118876980.5</t>
         </is>
       </c>
-      <c r="AZ17" t="inlineStr">
-        <is>
-          <t>14614553602.28</t>
-        </is>
+      <c r="AZ17" t="n">
+        <v>14614553602.28</v>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
@@ -7682,8 +7580,10 @@
           <t>82113231.98530579</t>
         </is>
       </c>
-      <c r="BD17" t="n">
-        <v>15812987742</v>
+      <c r="BD17" t="inlineStr">
+        <is>
+          <t>15812987742.0</t>
+        </is>
       </c>
       <c r="BE17" t="inlineStr">
         <is>
@@ -7849,7 +7749,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -8033,15 +7933,11 @@
           <t>916.8</t>
         </is>
       </c>
-      <c r="AM18" t="inlineStr">
-        <is>
-          <t>977.55</t>
-        </is>
-      </c>
-      <c r="AN18" t="inlineStr">
-        <is>
-          <t>938.52</t>
-        </is>
+      <c r="AM18" t="n">
+        <v>977.55</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>938.52</v>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
@@ -8088,20 +7984,16 @@
           <t>15882778006.0</t>
         </is>
       </c>
-      <c r="AX18" t="inlineStr">
-        <is>
-          <t>13620510362.4</t>
-        </is>
+      <c r="AX18" t="n">
+        <v>13620510362.4</v>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
           <t>12470961715.4</t>
         </is>
       </c>
-      <c r="AZ18" t="inlineStr">
-        <is>
-          <t>14466055493.78</t>
-        </is>
+      <c r="AZ18" t="n">
+        <v>14466055493.78</v>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
@@ -8118,8 +8010,10 @@
           <t>-123505858.3299389</t>
         </is>
       </c>
-      <c r="BD18" t="n">
-        <v>15882778006</v>
+      <c r="BD18" t="inlineStr">
+        <is>
+          <t>15882778006.0</t>
+        </is>
       </c>
       <c r="BE18" t="inlineStr">
         <is>
@@ -8285,7 +8179,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -8469,15 +8363,11 @@
           <t>917.6</t>
         </is>
       </c>
-      <c r="AM19" t="inlineStr">
-        <is>
-          <t>980.85</t>
-        </is>
-      </c>
-      <c r="AN19" t="inlineStr">
-        <is>
-          <t>933.96</t>
-        </is>
+      <c r="AM19" t="n">
+        <v>980.85</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>933.96</v>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
@@ -8524,20 +8414,16 @@
           <t>10973548400.0</t>
         </is>
       </c>
-      <c r="AX19" t="inlineStr">
-        <is>
-          <t>12590700418.8</t>
-        </is>
+      <c r="AX19" t="n">
+        <v>12590700418.8</v>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
           <t>11918833012.0</t>
         </is>
       </c>
-      <c r="AZ19" t="inlineStr">
-        <is>
-          <t>14368721493.28</t>
-        </is>
+      <c r="AZ19" t="n">
+        <v>14368721493.28</v>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
@@ -8554,8 +8440,10 @@
           <t>-420314020.6970749</t>
         </is>
       </c>
-      <c r="BD19" t="n">
-        <v>10973548400</v>
+      <c r="BD19" t="inlineStr">
+        <is>
+          <t>10973548400.0</t>
+        </is>
       </c>
       <c r="BE19" t="inlineStr">
         <is>
@@ -8721,7 +8609,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -8905,15 +8793,11 @@
           <t>932.2</t>
         </is>
       </c>
-      <c r="AM20" t="inlineStr">
-        <is>
-          <t>987.15</t>
-        </is>
-      </c>
-      <c r="AN20" t="inlineStr">
-        <is>
-          <t>929.9</t>
-        </is>
+      <c r="AM20" t="n">
+        <v>987.15</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>929.9</v>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
@@ -8960,20 +8844,16 @@
           <t>12353712685.0</t>
         </is>
       </c>
-      <c r="AX20" t="inlineStr">
-        <is>
-          <t>13187701378.4</t>
-        </is>
+      <c r="AX20" t="n">
+        <v>13187701378.4</v>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
           <t>12539817288.3</t>
         </is>
       </c>
-      <c r="AZ20" t="inlineStr">
-        <is>
-          <t>14292572173.18</t>
-        </is>
+      <c r="AZ20" t="n">
+        <v>14292572173.18</v>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
@@ -8990,8 +8870,10 @@
           <t>-303325579.8395176</t>
         </is>
       </c>
-      <c r="BD20" t="n">
-        <v>12353712685</v>
+      <c r="BD20" t="inlineStr">
+        <is>
+          <t>12353712685.0</t>
+        </is>
       </c>
       <c r="BE20" t="inlineStr">
         <is>
@@ -9157,7 +9039,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -9341,15 +9223,11 @@
           <t>947.0</t>
         </is>
       </c>
-      <c r="AM21" t="inlineStr">
-        <is>
-          <t>993.0</t>
-        </is>
-      </c>
-      <c r="AN21" t="inlineStr">
-        <is>
-          <t>925.54</t>
-        </is>
+      <c r="AM21" t="n">
+        <v>993</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>925.54</v>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
@@ -9396,20 +9274,16 @@
           <t>10709769939.0</t>
         </is>
       </c>
-      <c r="AX21" t="inlineStr">
-        <is>
-          <t>12964522972.0</t>
-        </is>
+      <c r="AX21" t="n">
+        <v>12964522972</v>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
           <t>13184192924.4</t>
         </is>
       </c>
-      <c r="AZ21" t="inlineStr">
-        <is>
-          <t>14209168625.62</t>
-        </is>
+      <c r="AZ21" t="n">
+        <v>14209168625.62</v>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
@@ -9426,8 +9300,10 @@
           <t>-273240924.15588</t>
         </is>
       </c>
-      <c r="BD21" t="n">
-        <v>10709769939</v>
+      <c r="BD21" t="inlineStr">
+        <is>
+          <t>10709769939.0</t>
+        </is>
       </c>
       <c r="BE21" t="inlineStr">
         <is>
@@ -9593,7 +9469,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -9777,15 +9653,11 @@
           <t>960.2</t>
         </is>
       </c>
-      <c r="AM22" t="inlineStr">
-        <is>
-          <t>997.15</t>
-        </is>
-      </c>
-      <c r="AN22" t="inlineStr">
-        <is>
-          <t>920.92</t>
-        </is>
+      <c r="AM22" t="n">
+        <v>997.15</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>920.92</v>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
@@ -9832,20 +9704,16 @@
           <t>18182742782.0</t>
         </is>
       </c>
-      <c r="AX22" t="inlineStr">
-        <is>
-          <t>13091194606.6</t>
-        </is>
+      <c r="AX22" t="n">
+        <v>13091194606.6</v>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
           <t>13748861147.6</t>
         </is>
       </c>
-      <c r="AZ22" t="inlineStr">
-        <is>
-          <t>14155319682.02</t>
-        </is>
+      <c r="AZ22" t="n">
+        <v>14155319682.02</v>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
@@ -9862,8 +9730,10 @@
           <t>-44367517.38797188</t>
         </is>
       </c>
-      <c r="BD22" t="n">
-        <v>18182742782</v>
+      <c r="BD22" t="inlineStr">
+        <is>
+          <t>18182742782.0</t>
+        </is>
       </c>
       <c r="BE22" t="inlineStr">
         <is>
@@ -10029,7 +9899,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -10213,15 +10083,11 @@
           <t>968.8</t>
         </is>
       </c>
-      <c r="AM23" t="inlineStr">
-        <is>
-          <t>1002.3</t>
-        </is>
-      </c>
-      <c r="AN23" t="inlineStr">
-        <is>
-          <t>916.24</t>
-        </is>
+      <c r="AM23" t="n">
+        <v>1002.3</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>916.24</v>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
@@ -10268,20 +10134,16 @@
           <t>10733728288.0</t>
         </is>
       </c>
-      <c r="AX23" t="inlineStr">
-        <is>
-          <t>11321413068.4</t>
-        </is>
+      <c r="AX23" t="n">
+        <v>11321413068.4</v>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
           <t>14033372540.0</t>
         </is>
       </c>
-      <c r="AZ23" t="inlineStr">
-        <is>
-          <t>13994353884.38</t>
-        </is>
+      <c r="AZ23" t="n">
+        <v>13994353884.38</v>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
@@ -10298,8 +10160,10 @@
           <t>-516496615.2771072</t>
         </is>
       </c>
-      <c r="BD23" t="n">
-        <v>10733728288</v>
+      <c r="BD23" t="inlineStr">
+        <is>
+          <t>10733728288.0</t>
+        </is>
       </c>
       <c r="BE23" t="inlineStr">
         <is>
@@ -10465,7 +10329,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -10649,15 +10513,11 @@
           <t>972.8</t>
         </is>
       </c>
-      <c r="AM24" t="inlineStr">
-        <is>
-          <t>1005.15</t>
-        </is>
-      </c>
-      <c r="AN24" t="inlineStr">
-        <is>
-          <t>911.3</t>
-        </is>
+      <c r="AM24" t="n">
+        <v>1005.15</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>911.3</v>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
@@ -10704,20 +10564,16 @@
           <t>13958553198.0</t>
         </is>
       </c>
-      <c r="AX24" t="inlineStr">
-        <is>
-          <t>11246965605.2</t>
-        </is>
+      <c r="AX24" t="n">
+        <v>11246965605.2</v>
       </c>
       <c r="AY24" t="inlineStr">
         <is>
           <t>15377407355.7</t>
         </is>
       </c>
-      <c r="AZ24" t="inlineStr">
-        <is>
-          <t>13940555876.02</t>
-        </is>
+      <c r="AZ24" t="n">
+        <v>13940555876.02</v>
       </c>
       <c r="BA24" t="inlineStr">
         <is>
@@ -10734,8 +10590,10 @@
           <t>-374411751.6445465</t>
         </is>
       </c>
-      <c r="BD24" t="n">
-        <v>13958553198</v>
+      <c r="BD24" t="inlineStr">
+        <is>
+          <t>13958553198.0</t>
+        </is>
       </c>
       <c r="BE24" t="inlineStr">
         <is>
@@ -10901,7 +10759,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -11085,15 +10943,11 @@
           <t>12.23</t>
         </is>
       </c>
-      <c r="AM25" t="inlineStr">
-        <is>
-          <t>12.33</t>
-        </is>
-      </c>
-      <c r="AN25" t="inlineStr">
-        <is>
-          <t>12.71</t>
-        </is>
+      <c r="AM25" t="n">
+        <v>12.33</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>12.71</v>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
@@ -11140,20 +10994,16 @@
           <t>4010000.0</t>
         </is>
       </c>
-      <c r="AX25" t="inlineStr">
-        <is>
-          <t>4538161.4</t>
-        </is>
+      <c r="AX25" t="n">
+        <v>4538161.4</v>
       </c>
       <c r="AY25" t="inlineStr">
         <is>
           <t>4658120.4</t>
         </is>
       </c>
-      <c r="AZ25" t="inlineStr">
-        <is>
-          <t>6264361.12</t>
-        </is>
+      <c r="AZ25" t="n">
+        <v>6264361.12</v>
       </c>
       <c r="BA25" t="inlineStr">
         <is>
@@ -11170,8 +11020,10 @@
           <t>-360898.6872821804</t>
         </is>
       </c>
-      <c r="BD25" t="n">
-        <v>4010000</v>
+      <c r="BD25" t="inlineStr">
+        <is>
+          <t>4010000.0</t>
+        </is>
       </c>
       <c r="BE25" t="inlineStr">
         <is>
@@ -11337,7 +11189,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -11521,15 +11373,11 @@
           <t>12.17</t>
         </is>
       </c>
-      <c r="AM26" t="inlineStr">
-        <is>
-          <t>12.35</t>
-        </is>
-      </c>
-      <c r="AN26" t="inlineStr">
-        <is>
-          <t>12.72</t>
-        </is>
+      <c r="AM26" t="n">
+        <v>12.35</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>12.72</v>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
@@ -11576,20 +11424,16 @@
           <t>4622403.0</t>
         </is>
       </c>
-      <c r="AX26" t="inlineStr">
-        <is>
-          <t>4644104.6</t>
-        </is>
+      <c r="AX26" t="n">
+        <v>4644104.6</v>
       </c>
       <c r="AY26" t="inlineStr">
         <is>
           <t>5156249.6</t>
         </is>
       </c>
-      <c r="AZ26" t="inlineStr">
-        <is>
-          <t>6337262.28</t>
-        </is>
+      <c r="AZ26" t="n">
+        <v>6337262.28</v>
       </c>
       <c r="BA26" t="inlineStr">
         <is>
@@ -11606,8 +11450,10 @@
           <t>-338995.6196279228</t>
         </is>
       </c>
-      <c r="BD26" t="n">
-        <v>4622403</v>
+      <c r="BD26" t="inlineStr">
+        <is>
+          <t>4622403.0</t>
+        </is>
       </c>
       <c r="BE26" t="inlineStr">
         <is>
@@ -11773,7 +11619,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -11957,15 +11803,11 @@
           <t>12.14</t>
         </is>
       </c>
-      <c r="AM27" t="inlineStr">
-        <is>
-          <t>12.38</t>
-        </is>
-      </c>
-      <c r="AN27" t="inlineStr">
-        <is>
-          <t>12.74</t>
-        </is>
+      <c r="AM27" t="n">
+        <v>12.38</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>12.74</v>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
@@ -12012,20 +11854,16 @@
           <t>2779771.0</t>
         </is>
       </c>
-      <c r="AX27" t="inlineStr">
-        <is>
-          <t>4768990.0</t>
-        </is>
+      <c r="AX27" t="n">
+        <v>4768990</v>
       </c>
       <c r="AY27" t="inlineStr">
         <is>
           <t>5068239.0</t>
         </is>
       </c>
-      <c r="AZ27" t="inlineStr">
-        <is>
-          <t>6335685.32</t>
-        </is>
+      <c r="AZ27" t="n">
+        <v>6335685.32</v>
       </c>
       <c r="BA27" t="inlineStr">
         <is>
@@ -12042,8 +11880,10 @@
           <t>-361213.1437065583</t>
         </is>
       </c>
-      <c r="BD27" t="n">
-        <v>2779771</v>
+      <c r="BD27" t="inlineStr">
+        <is>
+          <t>2779771.0</t>
+        </is>
       </c>
       <c r="BE27" t="inlineStr">
         <is>
@@ -12209,7 +12049,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -12393,15 +12233,11 @@
           <t>12.18</t>
         </is>
       </c>
-      <c r="AM28" t="inlineStr">
-        <is>
-          <t>12.42</t>
-        </is>
-      </c>
-      <c r="AN28" t="inlineStr">
-        <is>
-          <t>12.76</t>
-        </is>
+      <c r="AM28" t="n">
+        <v>12.42</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>12.76</v>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
@@ -12448,20 +12284,16 @@
           <t>6010261.0</t>
         </is>
       </c>
-      <c r="AX28" t="inlineStr">
-        <is>
-          <t>5059956.6</t>
-        </is>
+      <c r="AX28" t="n">
+        <v>5059956.6</v>
       </c>
       <c r="AY28" t="inlineStr">
         <is>
           <t>5381246.9</t>
         </is>
       </c>
-      <c r="AZ28" t="inlineStr">
-        <is>
-          <t>6501480.56</t>
-        </is>
+      <c r="AZ28" t="n">
+        <v>6501480.56</v>
       </c>
       <c r="BA28" t="inlineStr">
         <is>
@@ -12478,8 +12310,10 @@
           <t>-182627.1372579457</t>
         </is>
       </c>
-      <c r="BD28" t="n">
-        <v>6010261</v>
+      <c r="BD28" t="inlineStr">
+        <is>
+          <t>6010261.0</t>
+        </is>
       </c>
       <c r="BE28" t="inlineStr">
         <is>
@@ -12645,7 +12479,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -12829,15 +12663,11 @@
           <t>12.29</t>
         </is>
       </c>
-      <c r="AM29" t="inlineStr">
-        <is>
-          <t>12.48</t>
-        </is>
-      </c>
-      <c r="AN29" t="inlineStr">
-        <is>
-          <t>12.78</t>
-        </is>
+      <c r="AM29" t="n">
+        <v>12.48</v>
+      </c>
+      <c r="AN29" t="n">
+        <v>12.78</v>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
@@ -12884,20 +12714,16 @@
           <t>5268372.0</t>
         </is>
       </c>
-      <c r="AX29" t="inlineStr">
-        <is>
-          <t>5016336.8</t>
-        </is>
+      <c r="AX29" t="n">
+        <v>5016336.8</v>
       </c>
       <c r="AY29" t="inlineStr">
         <is>
           <t>5619133.3</t>
         </is>
       </c>
-      <c r="AZ29" t="inlineStr">
-        <is>
-          <t>6451329.98</t>
-        </is>
+      <c r="AZ29" t="n">
+        <v>6451329.98</v>
       </c>
       <c r="BA29" t="inlineStr">
         <is>
@@ -12914,8 +12740,10 @@
           <t>-267105.8017150005</t>
         </is>
       </c>
-      <c r="BD29" t="n">
-        <v>5268372</v>
+      <c r="BD29" t="inlineStr">
+        <is>
+          <t>5268372.0</t>
+        </is>
       </c>
       <c r="BE29" t="inlineStr">
         <is>
@@ -13081,7 +12909,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -13265,15 +13093,11 @@
           <t>12.33</t>
         </is>
       </c>
-      <c r="AM30" t="inlineStr">
-        <is>
-          <t>12.53</t>
-        </is>
-      </c>
-      <c r="AN30" t="inlineStr">
-        <is>
-          <t>12.8</t>
-        </is>
+      <c r="AM30" t="n">
+        <v>12.53</v>
+      </c>
+      <c r="AN30" t="n">
+        <v>12.8</v>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
@@ -13320,20 +13144,16 @@
           <t>4539716.0</t>
         </is>
       </c>
-      <c r="AX30" t="inlineStr">
-        <is>
-          <t>4778079.4</t>
-        </is>
+      <c r="AX30" t="n">
+        <v>4778079.4</v>
       </c>
       <c r="AY30" t="inlineStr">
         <is>
           <t>5511657.1</t>
         </is>
       </c>
-      <c r="AZ30" t="inlineStr">
-        <is>
-          <t>6434740.3</t>
-        </is>
+      <c r="AZ30" t="n">
+        <v>6434740.3</v>
       </c>
       <c r="BA30" t="inlineStr">
         <is>
@@ -13350,8 +13170,10 @@
           <t>-298762.0080209719</t>
         </is>
       </c>
-      <c r="BD30" t="n">
-        <v>4539716</v>
+      <c r="BD30" t="inlineStr">
+        <is>
+          <t>4539716.0</t>
+        </is>
       </c>
       <c r="BE30" t="inlineStr">
         <is>
@@ -13517,7 +13339,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -13701,15 +13523,11 @@
           <t>12.4</t>
         </is>
       </c>
-      <c r="AM31" t="inlineStr">
-        <is>
-          <t>12.59</t>
-        </is>
-      </c>
-      <c r="AN31" t="inlineStr">
-        <is>
-          <t>12.82</t>
-        </is>
+      <c r="AM31" t="n">
+        <v>12.59</v>
+      </c>
+      <c r="AN31" t="n">
+        <v>12.82</v>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
@@ -13756,20 +13574,16 @@
           <t>5246830.0</t>
         </is>
       </c>
-      <c r="AX31" t="inlineStr">
-        <is>
-          <t>5668394.6</t>
-        </is>
+      <c r="AX31" t="n">
+        <v>5668394.6</v>
       </c>
       <c r="AY31" t="inlineStr">
         <is>
           <t>5715593.1</t>
         </is>
       </c>
-      <c r="AZ31" t="inlineStr">
-        <is>
-          <t>6498115.24</t>
-        </is>
+      <c r="AZ31" t="n">
+        <v>6498115.24</v>
       </c>
       <c r="BA31" t="inlineStr">
         <is>
@@ -13786,8 +13600,10 @@
           <t>-255244.8024573242</t>
         </is>
       </c>
-      <c r="BD31" t="n">
-        <v>5246830</v>
+      <c r="BD31" t="inlineStr">
+        <is>
+          <t>5246830.0</t>
+        </is>
       </c>
       <c r="BE31" t="inlineStr">
         <is>
@@ -13953,7 +13769,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -14137,15 +13953,11 @@
           <t>12.41</t>
         </is>
       </c>
-      <c r="AM32" t="inlineStr">
-        <is>
-          <t>12.64</t>
-        </is>
-      </c>
-      <c r="AN32" t="inlineStr">
-        <is>
-          <t>12.84</t>
-        </is>
+      <c r="AM32" t="n">
+        <v>12.64</v>
+      </c>
+      <c r="AN32" t="n">
+        <v>12.84</v>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
@@ -14192,20 +14004,16 @@
           <t>4234604.0</t>
         </is>
       </c>
-      <c r="AX32" t="inlineStr">
-        <is>
-          <t>5367488.0</t>
-        </is>
+      <c r="AX32" t="n">
+        <v>5367488</v>
       </c>
       <c r="AY32" t="inlineStr">
         <is>
           <t>5751930.9</t>
         </is>
       </c>
-      <c r="AZ32" t="inlineStr">
-        <is>
-          <t>6479416.94</t>
-        </is>
+      <c r="AZ32" t="n">
+        <v>6479416.94</v>
       </c>
       <c r="BA32" t="inlineStr">
         <is>
@@ -14222,8 +14030,10 @@
           <t>-259723.6944214934</t>
         </is>
       </c>
-      <c r="BD32" t="n">
-        <v>4234604</v>
+      <c r="BD32" t="inlineStr">
+        <is>
+          <t>4234604.0</t>
+        </is>
       </c>
       <c r="BE32" t="inlineStr">
         <is>
@@ -14389,7 +14199,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -14573,15 +14383,11 @@
           <t>12.36</t>
         </is>
       </c>
-      <c r="AM33" t="inlineStr">
-        <is>
-          <t>12.68</t>
-        </is>
-      </c>
-      <c r="AN33" t="inlineStr">
-        <is>
-          <t>12.85</t>
-        </is>
+      <c r="AM33" t="n">
+        <v>12.68</v>
+      </c>
+      <c r="AN33" t="n">
+        <v>12.85</v>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
@@ -14628,20 +14434,16 @@
           <t>5792162.0</t>
         </is>
       </c>
-      <c r="AX33" t="inlineStr">
-        <is>
-          <t>5702537.2</t>
-        </is>
+      <c r="AX33" t="n">
+        <v>5702537.2</v>
       </c>
       <c r="AY33" t="inlineStr">
         <is>
           <t>6410566.5</t>
         </is>
       </c>
-      <c r="AZ33" t="inlineStr">
-        <is>
-          <t>6478982.52</t>
-        </is>
+      <c r="AZ33" t="n">
+        <v>6478982.52</v>
       </c>
       <c r="BA33" t="inlineStr">
         <is>
@@ -14658,8 +14460,10 @@
           <t>-148393.4795695404</t>
         </is>
       </c>
-      <c r="BD33" t="n">
-        <v>5792162</v>
+      <c r="BD33" t="inlineStr">
+        <is>
+          <t>5792162.0</t>
+        </is>
       </c>
       <c r="BE33" t="inlineStr">
         <is>
@@ -14825,7 +14629,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -15009,15 +14813,11 @@
           <t>12.29</t>
         </is>
       </c>
-      <c r="AM34" t="inlineStr">
-        <is>
-          <t>12.69</t>
-        </is>
-      </c>
-      <c r="AN34" t="inlineStr">
-        <is>
-          <t>12.86</t>
-        </is>
+      <c r="AM34" t="n">
+        <v>12.69</v>
+      </c>
+      <c r="AN34" t="n">
+        <v>12.86</v>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
@@ -15064,20 +14864,16 @@
           <t>4077085.0</t>
         </is>
       </c>
-      <c r="AX34" t="inlineStr">
-        <is>
-          <t>6221929.8</t>
-        </is>
+      <c r="AX34" t="n">
+        <v>6221929.8</v>
       </c>
       <c r="AY34" t="inlineStr">
         <is>
           <t>6227738.8</t>
         </is>
       </c>
-      <c r="AZ34" t="inlineStr">
-        <is>
-          <t>6456842.22</t>
-        </is>
+      <c r="AZ34" t="n">
+        <v>6456842.22</v>
       </c>
       <c r="BA34" t="inlineStr">
         <is>
@@ -15094,8 +14890,10 @@
           <t>-150931.762653552</t>
         </is>
       </c>
-      <c r="BD34" t="n">
-        <v>4077085</v>
+      <c r="BD34" t="inlineStr">
+        <is>
+          <t>4077085.0</t>
+        </is>
       </c>
       <c r="BE34" t="inlineStr">
         <is>
@@ -15261,7 +15059,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -15445,15 +15243,11 @@
           <t>12.27</t>
         </is>
       </c>
-      <c r="AM35" t="inlineStr">
-        <is>
-          <t>12.71</t>
-        </is>
-      </c>
-      <c r="AN35" t="inlineStr">
-        <is>
-          <t>12.87</t>
-        </is>
+      <c r="AM35" t="n">
+        <v>12.71</v>
+      </c>
+      <c r="AN35" t="n">
+        <v>12.87</v>
       </c>
       <c r="AO35" t="inlineStr">
         <is>
@@ -15500,20 +15294,16 @@
           <t>8991292.0</t>
         </is>
       </c>
-      <c r="AX35" t="inlineStr">
-        <is>
-          <t>6245234.8</t>
-        </is>
+      <c r="AX35" t="n">
+        <v>6245234.8</v>
       </c>
       <c r="AY35" t="inlineStr">
         <is>
           <t>6486688.9</t>
         </is>
       </c>
-      <c r="AZ35" t="inlineStr">
-        <is>
-          <t>6493450.2</t>
-        </is>
+      <c r="AZ35" t="n">
+        <v>6493450.2</v>
       </c>
       <c r="BA35" t="inlineStr">
         <is>
@@ -15530,8 +15320,10 @@
           <t>34590.78874977306</t>
         </is>
       </c>
-      <c r="BD35" t="n">
-        <v>8991292</v>
+      <c r="BD35" t="inlineStr">
+        <is>
+          <t>8991292.0</t>
+        </is>
       </c>
       <c r="BE35" t="inlineStr">
         <is>
